--- a/templates/SRI_OS_3_แจกแจงทรัพย์สิน.xlsx
+++ b/templates/SRI_OS_3_แจกแจงทรัพย์สิน.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t xml:space="preserve">SRI OS — แจกแจงทรัพย์สินต่อผู้ถือ</t>
   </si>
@@ -240,7 +240,13 @@
     <t xml:space="preserve">SRI Corporation</t>
   </si>
   <si>
-    <t xml:space="preserve">อสังหาริมทรัพย์เพื่อการลงทุน</t>
+    <t xml:space="preserve">อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการเช่า</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการขาย</t>
   </si>
   <si>
     <t xml:space="preserve">1510</t>
@@ -253,6 +259,12 @@
   </si>
   <si>
     <t xml:space="preserve">เงินให้กู้ยืม - เงินต้น</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เงินให้กู้ยืมแบบมีสินทรัพย์ค้ำประกัน - เงินต้น</t>
   </si>
   <si>
     <t xml:space="preserve">1400</t>
@@ -702,7 +714,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J255"/>
+  <dimension ref="A1:J267"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2695,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="G210" s="13">
-        <f>$E210+SUMIF($A$6:$A$205,$A210,$F$6:$F$205)</f>
+        <f>$E210</f>
         <v>0</v>
       </c>
       <c r="H210" s="15"/>
@@ -2731,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="G211" s="13">
-        <f>$E211</f>
+        <f>$E211+SUMIF($A$6:$A$205,$A211,$F$6:$F$205)</f>
         <v>0</v>
       </c>
       <c r="H211" s="15"/>
@@ -2854,13 +2866,13 @@
     </row>
     <row r="215">
       <c r="A215" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B215" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B215" s="12" t="s">
-        <v>59</v>
-      </c>
       <c r="C215" s="12" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D215" s="14">
         <f>COUNTIFS($A$6:$A$205,$A215,$D$6:$D$205,$B215)</f>
@@ -2890,13 +2902,13 @@
     </row>
     <row r="216">
       <c r="A216" s="12" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B216" s="12" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D216" s="14">
         <f>COUNTIFS($A$6:$A$205,$A216,$D$6:$D$205,$B216)</f>
@@ -2911,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="G216" s="13">
-        <f>$E216+SUMIF($A$6:$A$205,$A216,$F$6:$F$205)</f>
+        <f>$E216</f>
         <v>0</v>
       </c>
       <c r="H216" s="15"/>
@@ -2926,13 +2938,13 @@
     </row>
     <row r="217">
       <c r="A217" s="12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B217" s="12" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D217" s="14">
         <f>COUNTIFS($A$6:$A$205,$A217,$D$6:$D$205,$B217)</f>
@@ -2962,13 +2974,13 @@
     </row>
     <row r="218">
       <c r="A218" s="12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B218" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D218" s="14">
         <f>COUNTIFS($A$6:$A$205,$A218,$D$6:$D$205,$B218)</f>
@@ -2998,13 +3010,13 @@
     </row>
     <row r="219">
       <c r="A219" s="12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B219" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D219" s="14">
         <f>COUNTIFS($A$6:$A$205,$A219,$D$6:$D$205,$B219)</f>
@@ -3019,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="G219" s="13">
-        <f>$E219</f>
+        <f>$E219+SUMIF($A$6:$A$205,$A219,$F$6:$F$205)</f>
         <v>0</v>
       </c>
       <c r="H219" s="15"/>
@@ -3034,13 +3046,13 @@
     </row>
     <row r="220">
       <c r="A220" s="12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B220" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D220" s="14">
         <f>COUNTIFS($A$6:$A$205,$A220,$D$6:$D$205,$B220)</f>
@@ -3070,33 +3082,31 @@
     </row>
     <row r="221">
       <c r="A221" s="12" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B221" s="12" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D221" s="14">
         <f>COUNTIFS($A$6:$A$205,$A221,$D$6:$D$205,$B221)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E221" s="13">
         <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A221,$D$6:$D$205,$B221)</f>
-        <v>8000000</v>
+        <v>0</v>
       </c>
       <c r="F221" s="13">
         <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A221,$D$6:$D$205,$B221)</f>
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G221" s="13">
         <f>$E221</f>
-        <v>8000000</v>
-      </c>
-      <c r="H221" s="15">
-        <v>8000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H221" s="15"/>
       <c r="I221" s="13">
         <f>IF(AND($H221="",$G221=0),0,$H221-$G221)</f>
         <v>0</v>
@@ -3108,13 +3118,13 @@
     </row>
     <row r="222">
       <c r="A222" s="12" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B222" s="12" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D222" s="14">
         <f>COUNTIFS($A$6:$A$205,$A222,$D$6:$D$205,$B222)</f>
@@ -3129,12 +3139,10 @@
         <v>0</v>
       </c>
       <c r="G222" s="13">
-        <f>$E222+SUMIF($A$6:$A$205,$A222,$F$6:$F$205)</f>
-        <v>500000</v>
-      </c>
-      <c r="H222" s="15">
-        <v>500000</v>
-      </c>
+        <f>$E222</f>
+        <v>0</v>
+      </c>
+      <c r="H222" s="15"/>
       <c r="I222" s="13">
         <f>IF(AND($H222="",$G222=0),0,$H222-$G222)</f>
         <v>0</v>
@@ -3146,13 +3154,13 @@
     </row>
     <row r="223">
       <c r="A223" s="12" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B223" s="12" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D223" s="14">
         <f>COUNTIFS($A$6:$A$205,$A223,$D$6:$D$205,$B223)</f>
@@ -3182,13 +3190,13 @@
     </row>
     <row r="224">
       <c r="A224" s="12" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B224" s="12" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D224" s="14">
         <f>COUNTIFS($A$6:$A$205,$A224,$D$6:$D$205,$B224)</f>
@@ -3221,28 +3229,30 @@
         <v>56</v>
       </c>
       <c r="B225" s="12" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C225" s="12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D225" s="14">
         <f>COUNTIFS($A$6:$A$205,$A225,$D$6:$D$205,$B225)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E225" s="13">
         <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A225,$D$6:$D$205,$B225)</f>
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="F225" s="13">
         <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A225,$D$6:$D$205,$B225)</f>
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G225" s="13">
         <f>$E225</f>
-        <v>0</v>
-      </c>
-      <c r="H225" s="15"/>
+        <v>8000000</v>
+      </c>
+      <c r="H225" s="15">
+        <v>8000000</v>
+      </c>
       <c r="I225" s="13">
         <f>IF(AND($H225="",$G225=0),0,$H225-$G225)</f>
         <v>0</v>
@@ -3257,10 +3267,10 @@
         <v>56</v>
       </c>
       <c r="B226" s="12" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C226" s="12" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D226" s="14">
         <f>COUNTIFS($A$6:$A$205,$A226,$D$6:$D$205,$B226)</f>
@@ -3290,13 +3300,13 @@
     </row>
     <row r="227">
       <c r="A227" s="12" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B227" s="12" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C227" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D227" s="14">
         <f>COUNTIFS($A$6:$A$205,$A227,$D$6:$D$205,$B227)</f>
@@ -3311,10 +3321,12 @@
         <v>0</v>
       </c>
       <c r="G227" s="13">
-        <f>$E227</f>
-        <v>0</v>
-      </c>
-      <c r="H227" s="15"/>
+        <f>$E227+SUMIF($A$6:$A$205,$A227,$F$6:$F$205)</f>
+        <v>500000</v>
+      </c>
+      <c r="H227" s="15">
+        <v>500000</v>
+      </c>
       <c r="I227" s="13">
         <f>IF(AND($H227="",$G227=0),0,$H227-$G227)</f>
         <v>0</v>
@@ -3326,13 +3338,13 @@
     </row>
     <row r="228">
       <c r="A228" s="12" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B228" s="12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D228" s="14">
         <f>COUNTIFS($A$6:$A$205,$A228,$D$6:$D$205,$B228)</f>
@@ -3347,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="G228" s="13">
-        <f>$E228+SUMIF($A$6:$A$205,$A228,$F$6:$F$205)</f>
+        <f>$E228</f>
         <v>0</v>
       </c>
       <c r="H228" s="15"/>
@@ -3362,13 +3374,13 @@
     </row>
     <row r="229">
       <c r="A229" s="12" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B229" s="12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C229" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D229" s="14">
         <f>COUNTIFS($A$6:$A$205,$A229,$D$6:$D$205,$B229)</f>
@@ -3398,13 +3410,13 @@
     </row>
     <row r="230">
       <c r="A230" s="12" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B230" s="12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C230" s="12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D230" s="14">
         <f>COUNTIFS($A$6:$A$205,$A230,$D$6:$D$205,$B230)</f>
@@ -3434,13 +3446,13 @@
     </row>
     <row r="231">
       <c r="A231" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B231" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C231" s="12" t="s">
         <v>88</v>
-      </c>
-      <c r="B231" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C231" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="D231" s="14">
         <f>COUNTIFS($A$6:$A$205,$A231,$D$6:$D$205,$B231)</f>
@@ -3470,13 +3482,13 @@
     </row>
     <row r="232">
       <c r="A232" s="12" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B232" s="12" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C232" s="12" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D232" s="14">
         <f>COUNTIFS($A$6:$A$205,$A232,$D$6:$D$205,$B232)</f>
@@ -3506,7 +3518,7 @@
     </row>
     <row r="233">
       <c r="A233" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B233" s="12" t="s">
         <v>59</v>
@@ -3542,7 +3554,7 @@
     </row>
     <row r="234">
       <c r="A234" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B234" s="12" t="s">
         <v>77</v>
@@ -3563,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="G234" s="13">
-        <f>$E234+SUMIF($A$6:$A$205,$A234,$F$6:$F$205)</f>
+        <f>$E234</f>
         <v>0</v>
       </c>
       <c r="H234" s="15"/>
@@ -3578,7 +3590,7 @@
     </row>
     <row r="235">
       <c r="A235" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B235" s="12" t="s">
         <v>79</v>
@@ -3599,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="G235" s="13">
-        <f>$E235</f>
+        <f>$E235+SUMIF($A$6:$A$205,$A235,$F$6:$F$205)</f>
         <v>0</v>
       </c>
       <c r="H235" s="15"/>
@@ -3614,7 +3626,7 @@
     </row>
     <row r="236">
       <c r="A236" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B236" s="12" t="s">
         <v>81</v>
@@ -3650,7 +3662,7 @@
     </row>
     <row r="237">
       <c r="A237" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B237" s="12" t="s">
         <v>83</v>
@@ -3686,7 +3698,7 @@
     </row>
     <row r="238">
       <c r="A238" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B238" s="12" t="s">
         <v>85</v>
@@ -3722,13 +3734,13 @@
     </row>
     <row r="239">
       <c r="A239" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B239" s="12" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="C239" s="12" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D239" s="14">
         <f>COUNTIFS($A$6:$A$205,$A239,$D$6:$D$205,$B239)</f>
@@ -3758,13 +3770,13 @@
     </row>
     <row r="240">
       <c r="A240" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B240" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C240" s="12" t="s">
         <v>90</v>
-      </c>
-      <c r="B240" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C240" s="12" t="s">
-        <v>78</v>
       </c>
       <c r="D240" s="14">
         <f>COUNTIFS($A$6:$A$205,$A240,$D$6:$D$205,$B240)</f>
@@ -3779,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="G240" s="13">
-        <f>$E240+SUMIF($A$6:$A$205,$A240,$F$6:$F$205)</f>
+        <f>$E240</f>
         <v>0</v>
       </c>
       <c r="H240" s="15"/>
@@ -3794,13 +3806,13 @@
     </row>
     <row r="241">
       <c r="A241" s="12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B241" s="12" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C241" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D241" s="14">
         <f>COUNTIFS($A$6:$A$205,$A241,$D$6:$D$205,$B241)</f>
@@ -3830,13 +3842,13 @@
     </row>
     <row r="242">
       <c r="A242" s="12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B242" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C242" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D242" s="14">
         <f>COUNTIFS($A$6:$A$205,$A242,$D$6:$D$205,$B242)</f>
@@ -3866,13 +3878,13 @@
     </row>
     <row r="243">
       <c r="A243" s="12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B243" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C243" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D243" s="14">
         <f>COUNTIFS($A$6:$A$205,$A243,$D$6:$D$205,$B243)</f>
@@ -3887,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="G243" s="13">
-        <f>$E243</f>
+        <f>$E243+SUMIF($A$6:$A$205,$A243,$F$6:$F$205)</f>
         <v>0</v>
       </c>
       <c r="H243" s="15"/>
@@ -3902,13 +3914,13 @@
     </row>
     <row r="244">
       <c r="A244" s="12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B244" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C244" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D244" s="14">
         <f>COUNTIFS($A$6:$A$205,$A244,$D$6:$D$205,$B244)</f>
@@ -3936,116 +3948,548 @@
         <v>ตรงกัน</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B245" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C245" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D245" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A245,$D$6:$D$205,$B245)</f>
+        <v>0</v>
+      </c>
+      <c r="E245" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A245,$D$6:$D$205,$B245)</f>
+        <v>0</v>
+      </c>
+      <c r="F245" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A245,$D$6:$D$205,$B245)</f>
+        <v>0</v>
+      </c>
+      <c r="G245" s="13">
+        <f>$E245</f>
+        <v>0</v>
+      </c>
+      <c r="H245" s="15"/>
+      <c r="I245" s="13">
+        <f>IF(AND($H245="",$G245=0),0,$H245-$G245)</f>
+        <v>0</v>
+      </c>
+      <c r="J245" s="12" t="str">
+        <f>IF($I245=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
     <row r="246">
-      <c r="A246" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="247" ht="24" customHeight="1">
-      <c r="A247" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="B247" s="16"/>
-      <c r="C247" s="16"/>
-      <c r="D247" s="16"/>
-      <c r="E247" s="18">
+      <c r="A246" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B246" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C246" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D246" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A246,$D$6:$D$205,$B246)</f>
+        <v>0</v>
+      </c>
+      <c r="E246" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A246,$D$6:$D$205,$B246)</f>
+        <v>0</v>
+      </c>
+      <c r="F246" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A246,$D$6:$D$205,$B246)</f>
+        <v>0</v>
+      </c>
+      <c r="G246" s="13">
+        <f>$E246</f>
+        <v>0</v>
+      </c>
+      <c r="H246" s="15"/>
+      <c r="I246" s="13">
+        <f>IF(AND($H246="",$G246=0),0,$H246-$G246)</f>
+        <v>0</v>
+      </c>
+      <c r="J246" s="12" t="str">
+        <f>IF($I246=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B247" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C247" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D247" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A247,$D$6:$D$205,$B247)</f>
+        <v>0</v>
+      </c>
+      <c r="E247" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A247,$D$6:$D$205,$B247)</f>
+        <v>0</v>
+      </c>
+      <c r="F247" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A247,$D$6:$D$205,$B247)</f>
+        <v>0</v>
+      </c>
+      <c r="G247" s="13">
+        <f>$E247</f>
+        <v>0</v>
+      </c>
+      <c r="H247" s="15"/>
+      <c r="I247" s="13">
+        <f>IF(AND($H247="",$G247=0),0,$H247-$G247)</f>
+        <v>0</v>
+      </c>
+      <c r="J247" s="12" t="str">
+        <f>IF($I247=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B248" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C248" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D248" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A248,$D$6:$D$205,$B248)</f>
+        <v>0</v>
+      </c>
+      <c r="E248" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A248,$D$6:$D$205,$B248)</f>
+        <v>0</v>
+      </c>
+      <c r="F248" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A248,$D$6:$D$205,$B248)</f>
+        <v>0</v>
+      </c>
+      <c r="G248" s="13">
+        <f>$E248</f>
+        <v>0</v>
+      </c>
+      <c r="H248" s="15"/>
+      <c r="I248" s="13">
+        <f>IF(AND($H248="",$G248=0),0,$H248-$G248)</f>
+        <v>0</v>
+      </c>
+      <c r="J248" s="12" t="str">
+        <f>IF($I248=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B249" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C249" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D249" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A249,$D$6:$D$205,$B249)</f>
+        <v>0</v>
+      </c>
+      <c r="E249" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A249,$D$6:$D$205,$B249)</f>
+        <v>0</v>
+      </c>
+      <c r="F249" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A249,$D$6:$D$205,$B249)</f>
+        <v>0</v>
+      </c>
+      <c r="G249" s="13">
+        <f>$E249</f>
+        <v>0</v>
+      </c>
+      <c r="H249" s="15"/>
+      <c r="I249" s="13">
+        <f>IF(AND($H249="",$G249=0),0,$H249-$G249)</f>
+        <v>0</v>
+      </c>
+      <c r="J249" s="12" t="str">
+        <f>IF($I249=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B250" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C250" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D250" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A250,$D$6:$D$205,$B250)</f>
+        <v>0</v>
+      </c>
+      <c r="E250" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A250,$D$6:$D$205,$B250)</f>
+        <v>0</v>
+      </c>
+      <c r="F250" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A250,$D$6:$D$205,$B250)</f>
+        <v>0</v>
+      </c>
+      <c r="G250" s="13">
+        <f>$E250</f>
+        <v>0</v>
+      </c>
+      <c r="H250" s="15"/>
+      <c r="I250" s="13">
+        <f>IF(AND($H250="",$G250=0),0,$H250-$G250)</f>
+        <v>0</v>
+      </c>
+      <c r="J250" s="12" t="str">
+        <f>IF($I250=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B251" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C251" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D251" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A251,$D$6:$D$205,$B251)</f>
+        <v>0</v>
+      </c>
+      <c r="E251" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A251,$D$6:$D$205,$B251)</f>
+        <v>0</v>
+      </c>
+      <c r="F251" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A251,$D$6:$D$205,$B251)</f>
+        <v>0</v>
+      </c>
+      <c r="G251" s="13">
+        <f>$E251+SUMIF($A$6:$A$205,$A251,$F$6:$F$205)</f>
+        <v>0</v>
+      </c>
+      <c r="H251" s="15"/>
+      <c r="I251" s="13">
+        <f>IF(AND($H251="",$G251=0),0,$H251-$G251)</f>
+        <v>0</v>
+      </c>
+      <c r="J251" s="12" t="str">
+        <f>IF($I251=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B252" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C252" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D252" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A252,$D$6:$D$205,$B252)</f>
+        <v>0</v>
+      </c>
+      <c r="E252" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A252,$D$6:$D$205,$B252)</f>
+        <v>0</v>
+      </c>
+      <c r="F252" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A252,$D$6:$D$205,$B252)</f>
+        <v>0</v>
+      </c>
+      <c r="G252" s="13">
+        <f>$E252</f>
+        <v>0</v>
+      </c>
+      <c r="H252" s="15"/>
+      <c r="I252" s="13">
+        <f>IF(AND($H252="",$G252=0),0,$H252-$G252)</f>
+        <v>0</v>
+      </c>
+      <c r="J252" s="12" t="str">
+        <f>IF($I252=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B253" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C253" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D253" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A253,$D$6:$D$205,$B253)</f>
+        <v>0</v>
+      </c>
+      <c r="E253" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A253,$D$6:$D$205,$B253)</f>
+        <v>0</v>
+      </c>
+      <c r="F253" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A253,$D$6:$D$205,$B253)</f>
+        <v>0</v>
+      </c>
+      <c r="G253" s="13">
+        <f>$E253</f>
+        <v>0</v>
+      </c>
+      <c r="H253" s="15"/>
+      <c r="I253" s="13">
+        <f>IF(AND($H253="",$G253=0),0,$H253-$G253)</f>
+        <v>0</v>
+      </c>
+      <c r="J253" s="12" t="str">
+        <f>IF($I253=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B254" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C254" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D254" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A254,$D$6:$D$205,$B254)</f>
+        <v>0</v>
+      </c>
+      <c r="E254" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A254,$D$6:$D$205,$B254)</f>
+        <v>0</v>
+      </c>
+      <c r="F254" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A254,$D$6:$D$205,$B254)</f>
+        <v>0</v>
+      </c>
+      <c r="G254" s="13">
+        <f>$E254</f>
+        <v>0</v>
+      </c>
+      <c r="H254" s="15"/>
+      <c r="I254" s="13">
+        <f>IF(AND($H254="",$G254=0),0,$H254-$G254)</f>
+        <v>0</v>
+      </c>
+      <c r="J254" s="12" t="str">
+        <f>IF($I254=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B255" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C255" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D255" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A255,$D$6:$D$205,$B255)</f>
+        <v>0</v>
+      </c>
+      <c r="E255" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A255,$D$6:$D$205,$B255)</f>
+        <v>0</v>
+      </c>
+      <c r="F255" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A255,$D$6:$D$205,$B255)</f>
+        <v>0</v>
+      </c>
+      <c r="G255" s="13">
+        <f>$E255</f>
+        <v>0</v>
+      </c>
+      <c r="H255" s="15"/>
+      <c r="I255" s="13">
+        <f>IF(AND($H255="",$G255=0),0,$H255-$G255)</f>
+        <v>0</v>
+      </c>
+      <c r="J255" s="12" t="str">
+        <f>IF($I255=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B256" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C256" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D256" s="14">
+        <f>COUNTIFS($A$6:$A$205,$A256,$D$6:$D$205,$B256)</f>
+        <v>0</v>
+      </c>
+      <c r="E256" s="13">
+        <f>SUMIFS($E$6:$E$205,$A$6:$A$205,$A256,$D$6:$D$205,$B256)</f>
+        <v>0</v>
+      </c>
+      <c r="F256" s="13">
+        <f>SUMIFS($F$6:$F$205,$A$6:$A$205,$A256,$D$6:$D$205,$B256)</f>
+        <v>0</v>
+      </c>
+      <c r="G256" s="13">
+        <f>$E256</f>
+        <v>0</v>
+      </c>
+      <c r="H256" s="15"/>
+      <c r="I256" s="13">
+        <f>IF(AND($H256="",$G256=0),0,$H256-$G256)</f>
+        <v>0</v>
+      </c>
+      <c r="J256" s="12" t="str">
+        <f>IF($I256=0,"ตรงกัน","ต่างกัน — ต้องหา")</f>
+        <v>ตรงกัน</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="259" ht="24" customHeight="1">
+      <c r="A259" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B259" s="16"/>
+      <c r="C259" s="16"/>
+      <c r="D259" s="16"/>
+      <c r="E259" s="18">
         <f>COUNTIFS($E$6:$E$205,"&lt;&gt;",$A$6:$A$205,"")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="248" ht="24" customHeight="1">
-      <c r="A248" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B248" s="16"/>
-      <c r="C248" s="16"/>
-      <c r="D248" s="16"/>
-      <c r="E248" s="18">
+    <row r="260" ht="24" customHeight="1">
+      <c r="A260" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B260" s="16"/>
+      <c r="C260" s="16"/>
+      <c r="D260" s="16"/>
+      <c r="E260" s="18">
         <f>COUNTIFS($E$6:$E$205,"&lt;&gt;",$D$6:$D$205,"")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="249" ht="24" customHeight="1">
-      <c r="A249" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B249" s="16"/>
-      <c r="C249" s="16"/>
-      <c r="D249" s="16"/>
-      <c r="E249" s="18">
+    <row r="261" ht="24" customHeight="1">
+      <c r="A261" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B261" s="16"/>
+      <c r="C261" s="16"/>
+      <c r="D261" s="16"/>
+      <c r="E261" s="18">
         <f>COUNTA($A$6:$A$205)-SUMPRODUCT(COUNTIF($A$6:$A$205,{"SRI Corporation";"สุธี";"ธนากร";"ธนวินท์";"เบ็ญจพร";"สุดจิตต์"}))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="250" ht="24" customHeight="1">
-      <c r="A250" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B250" s="16"/>
-      <c r="C250" s="16"/>
-      <c r="D250" s="16"/>
-      <c r="E250" s="18">
-        <f>COUNTA($D$6:$D$205)-SUMPRODUCT(COUNTIF($D$6:$D$205,{"1500";"1510";"1300";"1400";"1410";"1600"}))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" ht="24" customHeight="1">
-      <c r="A251" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B251" s="16"/>
-      <c r="C251" s="16"/>
-      <c r="D251" s="16"/>
-      <c r="E251" s="17">
+    <row r="262" ht="24" customHeight="1">
+      <c r="A262" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B262" s="16"/>
+      <c r="C262" s="16"/>
+      <c r="D262" s="16"/>
+      <c r="E262" s="18">
+        <f>COUNTA($D$6:$D$205)-SUMPRODUCT(COUNTIF($D$6:$D$205,{"1500";"1520";"1510";"1300";"1320";"1400";"1410";"1600"}))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" ht="24" customHeight="1">
+      <c r="A263" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B263" s="16"/>
+      <c r="C263" s="16"/>
+      <c r="D263" s="16"/>
+      <c r="E263" s="17">
         <f>SUMIFS($F$6:$F$205,$D$6:$D$205,"1510")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="252" ht="24" customHeight="1">
-      <c r="A252" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B252" s="16"/>
-      <c r="C252" s="16"/>
-      <c r="D252" s="16"/>
-      <c r="E252" s="17">
-        <f>SUM($E$6:$E$205)-SUM($E$209:$E$244)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" ht="24" customHeight="1">
-      <c r="A253" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B253" s="16"/>
-      <c r="C253" s="16"/>
-      <c r="D253" s="16"/>
-      <c r="E253" s="17">
-        <f>SUM($F$6:$F$205)-SUM($F$209:$F$244)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" ht="24" customHeight="1">
-      <c r="A254" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B254" s="16"/>
-      <c r="C254" s="16"/>
-      <c r="D254" s="16"/>
-      <c r="E254" s="17">
-        <f>SUM($I$209:$I$244)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" ht="24" customHeight="1">
-      <c r="A255" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B255" s="16"/>
-      <c r="C255" s="16"/>
-      <c r="D255" s="16"/>
-      <c r="E255" s="18">
-        <f>COUNTIF($J$209:$J$244,"ต่างกัน*")</f>
+    <row r="264" ht="24" customHeight="1">
+      <c r="A264" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B264" s="16"/>
+      <c r="C264" s="16"/>
+      <c r="D264" s="16"/>
+      <c r="E264" s="17">
+        <f>SUM($E$6:$E$205)-SUM($E$209:$E$256)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" ht="24" customHeight="1">
+      <c r="A265" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B265" s="16"/>
+      <c r="C265" s="16"/>
+      <c r="D265" s="16"/>
+      <c r="E265" s="17">
+        <f>SUM($F$6:$F$205)-SUM($F$209:$F$256)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" ht="24" customHeight="1">
+      <c r="A266" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B266" s="16"/>
+      <c r="C266" s="16"/>
+      <c r="D266" s="16"/>
+      <c r="E266" s="17">
+        <f>SUM($I$209:$I$256)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" ht="24" customHeight="1">
+      <c r="A267" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B267" s="16"/>
+      <c r="C267" s="16"/>
+      <c r="D267" s="16"/>
+      <c r="E267" s="18">
+        <f>COUNTIF($J$209:$J$256,"ต่างกัน*")</f>
         <v>0</v>
       </c>
     </row>
@@ -4055,7 +4499,7 @@
       <formula1>"SRI Corporation,สุธี,ธนากร,ธนวินท์,เบ็ญจพร,สุดจิตต์"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" sqref="D6:D205">
-      <formula1>"1500,1510,1300,1400,1410,1600"</formula1>
+      <formula1>"1500,1520,1510,1300,1320,1400,1410,1600"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
